--- a/static/standards-correlations/Utah_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Utah_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$27</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | USBE CTE Strands and Standards, revised June 2025 - includes the new AI strand</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | USBE CTE Strands and Standards, revised June 2025 - includes the new AI strand</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -839,7 +840,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Most of the lifecycle is present and one phase is present unusually strongly, but neither the named ordered process nor the team roles appear. Define an algorithm is a stated Unit 1.1 objective. Top-down design is a stated Unit 1.2 objective and is named as a Unit 3.5 concept. Planning and design with documentation: Unit 3.5 plans before any code is written, Discovery Systems 4 draws the plan and argues for it, Ext 1.2B (Dependency Map) builds a dependency map. Implementation with comments: Unit 3.3. Testing: Units 2.2, 3.4, and 4.3. RELEASE AND MAINTENANCE is the strong one - Unit 5.3 publishes to a repository with a license and a README, and Ext 5.3B makes a second commit with a message and inspects the history, which is maintenance in the literal sense. ABSENT: the five team roles Utah names (team leader, analyst, senior developer, junior developer, client) and the SDLC as an ordered, named cycle.</t>
+          <t>Most of the lifecycle is present and one phase is present unusually strongly, but neither the named ordered process nor the team roles appear. Define an algorithm is a stated Unit 1.1 objective. Top-down design is a stated Unit 1.2 objective and is named as a Unit 3.5 concept. Planning and design with documentation: Unit 3.5 plans before any code is written, Introductory Systems 4 draws the plan and argues for it, Ext 1.2B (Dependency Map) builds a dependency map. Implementation with comments: Unit 3.3. Testing: Units 2.2, 3.4, and 4.3. RELEASE AND MAINTENANCE is the strong one - Unit 5.3 publishes to a repository with a license and a README, and Ext 5.3B makes a second commit with a message and inspects the history, which is maintenance in the literal sense. ABSENT: the five team roles Utah names (team leader, analyst, senior developer, junior developer, client) and the SDLC as an ordered, named cycle.</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1552,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>The strongest match in Strand 6, and all three bullets are evidenced. Impact of software on society: Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. covers copyright and piracy from the author's side, and Ext 2.6E (Automatic Data Collection) covers privacy through continuous automatic collection nobody approves individually. ETHICAL REASONS FOR RELIABLE AND ROBUST SOFTWARE is unusually well served - reliability is not an abstract virtue here but a stated design goal, with Unit 5.2 tagged reliability-oriented motor control, Unit 4.5 built on robust sequencing and error reset, and Unit 4.3 requiring defensive code. Automation and society: Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). plus Discovery Systems 12 on whose job it is to anticipate harm, and Ext 5.2D (Should It Exist?) requiring a credible-source judgment on whether a deployed system should exist.</t>
+          <t>The strongest match in Strand 6, and all three bullets are evidenced. Impact of software on society: Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. covers copyright and piracy from the author's side, and Ext 2.6E (Automatic Data Collection) covers privacy through continuous automatic collection nobody approves individually. ETHICAL REASONS FOR RELIABLE AND ROBUST SOFTWARE is unusually well served - reliability is not an abstract virtue here but a stated design goal, with Unit 5.2 tagged reliability-oriented motor control, Unit 4.5 built on robust sequencing and error reset, and Unit 4.3 requiring defensive code. Automation and society: Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). plus Introductory Systems 12 on whose job it is to anticipate harm, and Ext 5.2D (Should It Exist?) requiring a credible-source judgment on whether a deployed system should exist.</t>
         </is>
       </c>
     </row>
@@ -1663,6 +1664,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1707,7 +1709,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1721,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1843,6 +1845,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
@@ -1874,7 +1878,7 @@
 USBE contact: Kristina Yamada, CTE/Digital Technology Specialist.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT SHAPE: 14 Full, 7 Partial, 2 blank of 23. Touched 21 of 23.
   Strand 4 Control structures          4 Full of 4    - complete
